--- a/food_beverage_order_forms/024_girl_scout_cookie_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/024_girl_scout_cookie_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cookie_type</t>
+          <t>cookie_size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cookie Type</t>
+          <t>Cookie Size</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cookie_size</t>
+          <t>delivery_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cookie Size</t>
+          <t>Delivery Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Delivery Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cookie_type_options</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cookie Type</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cookie_size_options</t>
+          <t>delivery_date_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cookie Size</t>
+          <t>Delivery Date 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cookie_type</t>
+          <t>delivery_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cookie Type</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>first_order</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>heard_about</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>How Did You Hear About Us?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cookie_size</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cookie Size</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>payment_method_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Payment Method 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>delivery_date_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>delivery_time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Delivery Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>payment_method_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,508 +965,423 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cookie_type_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>oatmeal_raisin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Oatmeal Raisin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cookie_type_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>peanut_butter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Peanut Butter</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>chocolate_chip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chocolate Chip</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>shortbread</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Shortbread</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chocolate_chip</t>
+          <t>trefoil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chocolate Chip</t>
+          <t>Trefoil</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_order_form_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>oatmeal_raisin</t>
+          <t>lemon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oatmeal Raisin</t>
+          <t>Lemon</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_size_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>peanut_butter</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peanut Butter</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_size_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>peanut_butter_pandas</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peanut Butter Pandas</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_size_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>shortbread</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shortbread</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>cookie_size_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trefoil</t>
+          <t>half</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trefoil</t>
+          <t>Half</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cookie_type_options_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lemon</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cookie_size_options_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cookie_size_options_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cookie_size_options_choices</t>
+          <t>first_order_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cookie_size_options_choices</t>
+          <t>first_order_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Half</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cookie_type_choices</t>
+          <t>heard_about_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>oatmeal_raisin</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oatmeal Raisin</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cookie_type_choices</t>
+          <t>heard_about_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>peanut_butter</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peanut Butter</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>heard_about_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>heard_about_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>flyer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Flyer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cookie_size_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>credit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>paypal</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>payment_method_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>payment_method_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>credit</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>payment_method_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>paypal</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>PayPal</t>
         </is>
